--- a/main/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/main/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:40:33+00:00</t>
+    <t>2026-07-21T12:38:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DocumentReference</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DocumentReference|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -479,7 +479,7 @@
     <t>isEmergency</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-ext-is-emergency}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-ext-is-emergency|3.0.1}
 </t>
   </si>
   <si>
@@ -660,7 +660,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J23-TypeNoteCahierLiaison-CISIS/FHIR/JDV-J23-TypeNoteCahierLiaison-CISIS|20200424120000</t>
   </si>
   <si>
     <t>Note.type</t>
@@ -728,7 +728,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1)
 </t>
   </si>
   <si>
@@ -800,7 +800,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.0.1|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.0.1)
 </t>
   </si>
   <si>
@@ -1055,7 +1055,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS|20200424120000</t>
   </si>
   <si>
     <t>Note.restrictionAudience</t>
@@ -1430,7 +1430,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|3.0.0</t>
   </si>
   <si>
     <t>Composition.event.code</t>
@@ -1908,7 +1908,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.28515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="94.22265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="108.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/main/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:38:43+00:00</t>
+    <t>2026-07-21T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/main/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:31+00:00</t>
+    <t>2026-07-21T13:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-document-reference.xlsx
+++ b/main/ig/StructureDefinition-cdl-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:21:42+00:00</t>
+    <t>2026-07-21T13:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
